--- a/Figures/Binomial GLM/LD5_Table.xlsx
+++ b/Figures/Binomial GLM/LD5_Table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABerk\Documents\R\Github Repositories\phyto_synthesis\Figures\Binomial GAM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABerk\Documents\R\Github Repositories\phyto_synthesis\Figures\Binomial GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF07CA5-974E-4162-9CAA-88BDAE30E3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FAE9A6-8A59-4D2F-B379-851D2A0D4D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-2940" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,9 +55,6 @@
     <t>Parameter</t>
   </si>
   <si>
-    <t>μg/L</t>
-  </si>
-  <si>
     <t>μS/cm</t>
   </si>
   <si>
@@ -74,6 +71,9 @@
   </si>
   <si>
     <t>Threshold Values Resulting in 5% Chance of Phytoplankton Bloom</t>
+  </si>
+  <si>
+    <t>mg/L</t>
   </si>
 </sst>
 </file>
@@ -184,17 +184,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,20 +502,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
+      <c r="A1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="10" t="s">
-        <v>16</v>
+      <c r="B2" s="11"/>
+      <c r="C2" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="D2" s="7"/>
     </row>
@@ -524,13 +524,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3">
         <v>6.0562757882978803E-2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -538,13 +538,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3">
         <v>0.32510199966191899</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -552,7 +552,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3">
         <v>0.145907230574186</v>
@@ -564,13 +564,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3">
         <v>11851.6600129946</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>14</v>
+      <c r="D6" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -578,7 +578,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3">
         <v>121.849049059302</v>
@@ -590,13 +590,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3">
         <v>0.108933390238636</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -604,13 +604,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3">
         <v>0.47115097586055998</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -618,7 +618,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3">
         <v>0.12724209930852801</v>
@@ -630,13 +630,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3">
         <v>20332.832931834299</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -650,12 +650,12 @@
         <v>15.8208978539882</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>

--- a/Figures/Binomial GLM/LD5_Table.xlsx
+++ b/Figures/Binomial GLM/LD5_Table.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABerk\Documents\R\Github Repositories\phyto_synthesis\Figures\Binomial GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FAE9A6-8A59-4D2F-B379-851D2A0D4D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F2D9AA-CAD0-4474-925C-786F05274981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-2940" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$2:$D$12</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
   <si>
     <t>Temperature</t>
   </si>
@@ -74,6 +77,9 @@
   </si>
   <si>
     <t>mg/L</t>
+  </si>
+  <si>
+    <t>Lag DissAmmonia</t>
   </si>
 </sst>
 </file>
@@ -175,17 +181,11 @@
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -195,6 +195,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -211,6 +217,133 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2CE7DBF-53F9-6931-ADED-7DC3A848CD13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4752975" y="304800"/>
+          <a:ext cx="3962400" cy="2886075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{204473B2-90B0-AF3B-0F18-CF6261D3322A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4714875" y="3333750"/>
+          <a:ext cx="3962400" cy="2219325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -502,164 +635,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="11">
+        <v>15.8208978539882</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="11">
+        <v>121.849049059302</v>
+      </c>
+      <c r="D4" s="10"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C5" s="11">
+        <v>0.108933390238636</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.47115097586055998</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.12724209930852801</v>
+      </c>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="11">
+        <v>20332.832931834299</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="11">
         <v>6.0562757882978803E-2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D9" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C10" s="11">
         <v>0.32510199966191899</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D10" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C11" s="11">
         <v>0.145907230574186</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C12" s="3">
         <v>11851.6600129946</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D12" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3">
-        <v>121.849049059302</v>
-      </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.108933390238636</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0.47115097586055998</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0.12724209930852801</v>
-      </c>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="3">
-        <v>20332.832931834299</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>15.8208978539882</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -674,6 +807,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Figures/Binomial GLM/LD5_Table.xlsx
+++ b/Figures/Binomial GLM/LD5_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABerk\Documents\R\Github Repositories\phyto_synthesis\Figures\Binomial GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F2D9AA-CAD0-4474-925C-786F05274981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB5DACE-BBB8-458B-B572-35598B59E0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-2940" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>Temperature</t>
   </si>
@@ -64,12 +64,6 @@
     <t>cf/s</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Results are significant </t>
-  </si>
-  <si>
     <t xml:space="preserve">Threshold Value </t>
   </si>
   <si>
@@ -80,13 +74,28 @@
   </si>
   <si>
     <t>Lag DissAmmonia</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. Results are significant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. No value exists where predicted probability of a bloom is 5%. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -111,6 +120,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -187,6 +203,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -196,11 +214,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -224,22 +242,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>439616</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>304800</xdr:rowOff>
+      <xdr:rowOff>153865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>592016</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>163390</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2CE7DBF-53F9-6931-ADED-7DC3A848CD13}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19EE2EFE-8D41-D93C-023A-912FA1D77879}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -262,8 +280,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4752975" y="304800"/>
-          <a:ext cx="3962400" cy="2886075"/>
+          <a:off x="5158154" y="153865"/>
+          <a:ext cx="3962400" cy="3072179"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -285,22 +303,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>366346</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>102577</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>518746</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>35902</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{204473B2-90B0-AF3B-0F18-CF6261D3322A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AB124A4-B739-AC66-717A-FEE196963E50}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -323,7 +341,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4714875" y="3333750"/>
+          <a:off x="5084884" y="3546231"/>
           <a:ext cx="3962400" cy="2219325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -635,142 +653,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7">
+        <v>15.45362525</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="12">
+        <v>0.12247278</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="12">
+        <v>0.30294924000000001</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="12">
+        <v>20992.47041265</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="11">
-        <v>15.8208978539882</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="11">
-        <v>121.849049059302</v>
-      </c>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="C9" s="12">
+        <v>4.8832430000000003E-2</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0.30294924000000001</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="11">
-        <v>0.108933390238636</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="11">
-        <v>0.47115097586055998</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="11">
-        <v>0.12724209930852801</v>
-      </c>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="11">
-        <v>20332.832931834299</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="D11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="11">
-        <v>6.0562757882978803E-2</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="11">
-        <v>0.32510199966191899</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11">
-        <v>0.145907230574186</v>
-      </c>
-      <c r="D11" s="10"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -780,22 +804,24 @@
         <v>12</v>
       </c>
       <c r="C12" s="3">
-        <v>11851.6600129946</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>13</v>
+        <v>11799.18991126</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>

--- a/Figures/Binomial GLM/LD5_Table.xlsx
+++ b/Figures/Binomial GLM/LD5_Table.xlsx
@@ -811,6 +811,309 @@
 </worksheet>
 </file>
 
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CDF426C5941C634898DECC69F43B1B84" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60c32b66aab15ddd96dedd0d00727b31">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="a26c063d-e4ab-4c2c-a5f9-3b05989843c6" xmlns:ns3="73166ee1-6b64-49a2-af77-8563fe7cb853" xmlns:ns4="31062a0d-ede8-4112-b4bb-00a9c1bc8e16" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5af1b35808a5f3b2dd9f4924c89efa02" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
+    <xsd:import namespace="a26c063d-e4ab-4c2c-a5f9-3b05989843c6"/>
+    <xsd:import namespace="73166ee1-6b64-49a2-af77-8563fe7cb853"/>
+    <xsd:import namespace="31062a0d-ede8-4112-b4bb-00a9c1bc8e16"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="17" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a26c063d-e4ab-4c2c-a5f9-3b05989843c6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="9c5df3ad-b4e5-45d1-88c9-23db5f1fe618" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="73166ee1-6b64-49a2-af77-8563fe7cb853" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="15" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="16" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="31062a0d-ede8-4112-b4bb-00a9c1bc8e16" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{5171f4bf-df9e-4530-a04f-417f2293f133}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="73166ee1-6b64-49a2-af77-8563fe7cb853">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a26c063d-e4ab-4c2c-a5f9-3b05989843c6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="31062a0d-ede8-4112-b4bb-00a9c1bc8e16" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01C73FA8-F1F9-49CD-82DE-B389E9576FC4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D76EFA6-844A-4DA7-BEBD-687A79FB44D5}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29B09617-3BBF-4CA7-B2E9-F9A09E393409}"/>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0bb6ca0c-ccb3-428b-9d5f-a9c60cad6645}" enabled="1" method="Standard" siteId="{fe186a25-7d49-41e6-9941-05d2281d36c1}" contentBits="0" removed="0"/>

--- a/Figures/Binomial GLM/LD5_Table.xlsx
+++ b/Figures/Binomial GLM/LD5_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ABerk\Documents\R\Github Repositories\phyto_synthesis\Figures\Binomial GLM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F2D9AA-CAD0-4474-925C-786F05274981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617E1F55-9C46-49A2-B4FE-FB3CD3B1A475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-2940" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>Temperature</t>
   </si>
@@ -64,12 +64,6 @@
     <t>cf/s</t>
   </si>
   <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Results are significant </t>
-  </si>
-  <si>
     <t xml:space="preserve">Threshold Value </t>
   </si>
   <si>
@@ -80,13 +74,28 @@
   </si>
   <si>
     <t>Lag DissAmmonia</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a. Results are significant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b. No value exists where predicted probability of a bloom is 5%. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -111,6 +120,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -187,6 +203,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -196,11 +214,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,142 +653,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7">
+        <v>15.46362525</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.12247278</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.48907457999999998</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7">
+        <v>20992.47041265</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="11">
-        <v>15.8208978539882</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="11">
-        <v>121.849049059302</v>
-      </c>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="C9" s="7">
+        <v>4.8832430000000003E-2</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.30294924000000001</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="11">
-        <v>0.108933390238636</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="11">
-        <v>0.47115097586055998</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="11">
-        <v>0.12724209930852801</v>
-      </c>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="11">
-        <v>20332.832931834299</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="11">
-        <v>6.0562757882978803E-2</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="11">
-        <v>0.32510199966191899</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11">
-        <v>0.145907230574186</v>
-      </c>
-      <c r="D11" s="10"/>
+      <c r="D11" s="12" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
@@ -780,22 +804,24 @@
         <v>12</v>
       </c>
       <c r="C12" s="3">
-        <v>11851.6600129946</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>13</v>
+        <v>11799.18991126</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -812,6 +838,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a26c063d-e4ab-4c2c-a5f9-3b05989843c6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="31062a0d-ede8-4112-b4bb-00a9c1bc8e16" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CDF426C5941C634898DECC69F43B1B84" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="60c32b66aab15ddd96dedd0d00727b31">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="a26c063d-e4ab-4c2c-a5f9-3b05989843c6" xmlns:ns3="73166ee1-6b64-49a2-af77-8563fe7cb853" xmlns:ns4="31062a0d-ede8-4112-b4bb-00a9c1bc8e16" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5af1b35808a5f3b2dd9f4924c89efa02" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1080,38 +1128,45 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29B09617-3BBF-4CA7-B2E9-F9A09E393409}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="a26c063d-e4ab-4c2c-a5f9-3b05989843c6"/>
+    <ds:schemaRef ds:uri="31062a0d-ede8-4112-b4bb-00a9c1bc8e16"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a26c063d-e4ab-4c2c-a5f9-3b05989843c6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="31062a0d-ede8-4112-b4bb-00a9c1bc8e16" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D76EFA6-844A-4DA7-BEBD-687A79FB44D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01C73FA8-F1F9-49CD-82DE-B389E9576FC4}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D76EFA6-844A-4DA7-BEBD-687A79FB44D5}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29B09617-3BBF-4CA7-B2E9-F9A09E393409}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01C73FA8-F1F9-49CD-82DE-B389E9576FC4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="a26c063d-e4ab-4c2c-a5f9-3b05989843c6"/>
+    <ds:schemaRef ds:uri="73166ee1-6b64-49a2-af77-8563fe7cb853"/>
+    <ds:schemaRef ds:uri="31062a0d-ede8-4112-b4bb-00a9c1bc8e16"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
